--- a/Лаб.работа/Расчет эвольвентных шлицов.xlsx
+++ b/Лаб.работа/Расчет эвольвентных шлицов.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hulumulu\Desktop\Никита\Лаб.работа\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BMSTU Projects\ПКП\Лаб.работа\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{922F60C2-AE18-48CE-89A8-2B0E96B766A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EBEE6FD-51D0-43E9-882D-0CC50206328C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="3396" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="-20085" yWindow="1800" windowWidth="19245" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Расчет эвольвентных шлицов" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -183,7 +184,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="25">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -366,19 +367,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -525,7 +513,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -575,51 +563,48 @@
     <xf numFmtId="2" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="9" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="6" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -640,9 +625,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -680,9 +665,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -715,26 +700,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -767,26 +735,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -961,67 +912,67 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:P34"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.44140625" customWidth="1"/>
-    <col min="2" max="2" width="13.44140625" customWidth="1"/>
+    <col min="1" max="1" width="8.42578125" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="4" max="4" width="8.44140625" customWidth="1"/>
-    <col min="5" max="6" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.33203125" customWidth="1"/>
-    <col min="8" max="8" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.44140625" customWidth="1"/>
-    <col min="10" max="10" width="12.33203125" style="6" customWidth="1"/>
-    <col min="11" max="11" width="9.109375" style="6"/>
-    <col min="12" max="12" width="14.44140625" style="6" customWidth="1"/>
-    <col min="13" max="13" width="13.88671875" style="6" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" customWidth="1"/>
+    <col min="5" max="6" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.28515625" customWidth="1"/>
+    <col min="8" max="8" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.42578125" customWidth="1"/>
+    <col min="10" max="10" width="12.28515625" style="6" customWidth="1"/>
+    <col min="11" max="11" width="9.140625" style="6"/>
+    <col min="12" max="12" width="14.42578125" style="6" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:16" ht="30.6" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B2" s="22" t="s">
+    <row r="2" spans="2:16" ht="30.75" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B2" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="21">
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="20">
         <v>750</v>
       </c>
-      <c r="J2" s="21"/>
-    </row>
-    <row r="3" spans="2:16" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="27" t="s">
+      <c r="J2" s="20"/>
+    </row>
+    <row r="3" spans="2:16" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="29" t="s">
+      <c r="C3" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="31"/>
-      <c r="I3" s="32" t="s">
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="30"/>
+      <c r="I3" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="J3" s="23" t="s">
+      <c r="J3" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="K3" s="23" t="s">
+      <c r="K3" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="L3" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="M3" s="25" t="s">
+      <c r="L3" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="M3" s="24" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="2:16" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="28"/>
+    <row r="4" spans="2:16" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="27"/>
       <c r="C4" s="1">
         <v>0.8</v>
       </c>
@@ -1040,13 +991,13 @@
       <c r="H4" s="5">
         <v>8</v>
       </c>
-      <c r="I4" s="33"/>
-      <c r="J4" s="24"/>
-      <c r="K4" s="24"/>
-      <c r="L4" s="24"/>
-      <c r="M4" s="26"/>
-    </row>
-    <row r="5" spans="2:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I4" s="32"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
+      <c r="M4" s="25"/>
+    </row>
+    <row r="5" spans="2:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B5" s="8">
         <v>15</v>
       </c>
@@ -1054,11 +1005,11 @@
         <f>$B5-C$4*2</f>
         <v>13.4</v>
       </c>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="19"/>
       <c r="I5" s="9">
         <v>87</v>
       </c>
@@ -1069,7 +1020,6 @@
         <v>50</v>
       </c>
       <c r="L5" s="10">
-        <f>1.2*K5</f>
         <v>60</v>
       </c>
       <c r="M5" s="11">
@@ -1077,7 +1027,7 @@
         <v>143.67816091954023</v>
       </c>
     </row>
-    <row r="6" spans="2:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B6" s="12">
         <v>17</v>
       </c>
@@ -1102,8 +1052,7 @@
       <c r="K6" s="10">
         <v>50</v>
       </c>
-      <c r="L6" s="3">
-        <f t="shared" ref="L6:L34" si="1">1.2*K6</f>
+      <c r="L6" s="10">
         <v>60</v>
       </c>
       <c r="M6" s="13">
@@ -1111,7 +1060,7 @@
         <v>112.61261261261261</v>
       </c>
     </row>
-    <row r="7" spans="2:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B7" s="12">
         <v>20</v>
       </c>
@@ -1136,8 +1085,7 @@
       <c r="K7" s="10">
         <v>50</v>
       </c>
-      <c r="L7" s="3">
-        <f t="shared" si="1"/>
+      <c r="L7" s="10">
         <v>60</v>
       </c>
       <c r="M7" s="13">
@@ -1145,7 +1093,7 @@
         <v>81.699346405228752</v>
       </c>
     </row>
-    <row r="8" spans="2:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12">
         <v>25</v>
       </c>
@@ -1170,8 +1118,7 @@
       <c r="K8" s="10">
         <v>50</v>
       </c>
-      <c r="L8" s="3">
-        <f t="shared" si="1"/>
+      <c r="L8" s="10">
         <v>60</v>
       </c>
       <c r="M8" s="13">
@@ -1179,7 +1126,7 @@
         <v>49.800796812749006</v>
       </c>
     </row>
-    <row r="9" spans="2:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B9" s="12">
         <v>30</v>
       </c>
@@ -1204,8 +1151,7 @@
       <c r="K9" s="10">
         <v>50</v>
       </c>
-      <c r="L9" s="3">
-        <f t="shared" si="1"/>
+      <c r="L9" s="10">
         <v>60</v>
       </c>
       <c r="M9" s="13">
@@ -1213,7 +1159,7 @@
         <v>34.059945504087196</v>
       </c>
     </row>
-    <row r="10" spans="2:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B10" s="12">
         <v>35</v>
       </c>
@@ -1238,8 +1184,7 @@
       <c r="K10" s="10">
         <v>50</v>
       </c>
-      <c r="L10" s="3">
-        <f t="shared" si="1"/>
+      <c r="L10" s="10">
         <v>60</v>
       </c>
       <c r="M10" s="13">
@@ -1247,7 +1192,7 @@
         <v>25.826446280991735</v>
       </c>
     </row>
-    <row r="11" spans="2:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B11" s="12">
         <v>40</v>
       </c>
@@ -1267,21 +1212,20 @@
         <v>635</v>
       </c>
       <c r="J11" s="3">
-        <v>1</v>
+        <v>1.38</v>
       </c>
       <c r="K11" s="10">
         <v>50</v>
       </c>
-      <c r="L11" s="3">
-        <f t="shared" si="1"/>
+      <c r="L11" s="10">
         <v>60</v>
       </c>
       <c r="M11" s="13">
         <f>1000*I2*J11/(I11*L11)</f>
-        <v>19.685039370078741</v>
-      </c>
-    </row>
-    <row r="12" spans="2:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
+        <v>27.165354330708659</v>
+      </c>
+    </row>
+    <row r="12" spans="2:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B12" s="12">
         <v>45</v>
       </c>
@@ -1306,8 +1250,7 @@
       <c r="K12" s="10">
         <v>50</v>
       </c>
-      <c r="L12" s="3">
-        <f t="shared" si="1"/>
+      <c r="L12" s="10">
         <v>60</v>
       </c>
       <c r="M12" s="13">
@@ -1315,7 +1258,7 @@
         <v>15.151515151515152</v>
       </c>
     </row>
-    <row r="13" spans="2:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B13" s="12">
         <v>50</v>
       </c>
@@ -1340,8 +1283,7 @@
       <c r="K13" s="10">
         <v>50</v>
       </c>
-      <c r="L13" s="3">
-        <f t="shared" si="1"/>
+      <c r="L13" s="10">
         <v>60</v>
       </c>
       <c r="M13" s="13">
@@ -1349,7 +1291,7 @@
         <v>12.030798845043311</v>
       </c>
     </row>
-    <row r="14" spans="2:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B14" s="12">
         <v>55</v>
       </c>
@@ -1369,22 +1311,21 @@
         <v>1217</v>
       </c>
       <c r="J14" s="3">
-        <v>1</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="K14" s="10">
         <v>50</v>
       </c>
-      <c r="L14" s="3">
-        <f t="shared" si="1"/>
+      <c r="L14" s="10">
         <v>60</v>
       </c>
       <c r="M14" s="13">
         <f>1000*I2*J14/(I14*L14)</f>
-        <v>10.271158586688578</v>
-      </c>
-      <c r="P14" s="18"/>
-    </row>
-    <row r="15" spans="2:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
+        <v>5.7518488085456045</v>
+      </c>
+      <c r="P14" s="17"/>
+    </row>
+    <row r="15" spans="2:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B15" s="12">
         <v>60</v>
       </c>
@@ -1409,8 +1350,7 @@
       <c r="K15" s="10">
         <v>50</v>
       </c>
-      <c r="L15" s="3">
-        <f t="shared" si="1"/>
+      <c r="L15" s="10">
         <v>60</v>
       </c>
       <c r="M15" s="13">
@@ -1418,7 +1358,7 @@
         <v>8.7842586085734364</v>
       </c>
     </row>
-    <row r="16" spans="2:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B16" s="12">
         <v>65</v>
       </c>
@@ -1438,21 +1378,20 @@
         <v>1716</v>
       </c>
       <c r="J16" s="3">
-        <v>1</v>
+        <v>0.38</v>
       </c>
       <c r="K16" s="10">
         <v>50</v>
       </c>
-      <c r="L16" s="3">
-        <f t="shared" si="1"/>
+      <c r="L16" s="10">
         <v>60</v>
       </c>
       <c r="M16" s="13">
         <f>1000*I2*J16/(I16*L16)</f>
-        <v>7.2843822843822847</v>
-      </c>
-    </row>
-    <row r="17" spans="2:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
+        <v>2.7680652680652682</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B17" s="12">
         <v>70</v>
       </c>
@@ -1477,8 +1416,7 @@
       <c r="K17" s="10">
         <v>50</v>
       </c>
-      <c r="L17" s="3">
-        <f t="shared" si="1"/>
+      <c r="L17" s="10">
         <v>60</v>
       </c>
       <c r="M17" s="13">
@@ -1486,7 +1424,7 @@
         <v>6.1425061425061429</v>
       </c>
     </row>
-    <row r="18" spans="2:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B18" s="12">
         <v>75</v>
       </c>
@@ -1511,8 +1449,7 @@
       <c r="K18" s="10">
         <v>50</v>
       </c>
-      <c r="L18" s="3">
-        <f t="shared" si="1"/>
+      <c r="L18" s="10">
         <v>60</v>
       </c>
       <c r="M18" s="13">
@@ -1520,7 +1457,7 @@
         <v>5.3214133673903792</v>
       </c>
     </row>
-    <row r="19" spans="2:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B19" s="12">
         <v>80</v>
       </c>
@@ -1545,8 +1482,7 @@
       <c r="K19" s="10">
         <v>50</v>
       </c>
-      <c r="L19" s="3">
-        <f t="shared" si="1"/>
+      <c r="L19" s="10">
         <v>60</v>
       </c>
       <c r="M19" s="13">
@@ -1554,7 +1490,7 @@
         <v>4.7474363843524499</v>
       </c>
     </row>
-    <row r="20" spans="2:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B20" s="12">
         <v>85</v>
       </c>
@@ -1574,21 +1510,20 @@
         <v>2844</v>
       </c>
       <c r="J20" s="3">
-        <v>1</v>
+        <v>7.83</v>
       </c>
       <c r="K20" s="10">
         <v>50</v>
       </c>
-      <c r="L20" s="3">
-        <f t="shared" si="1"/>
+      <c r="L20" s="10">
         <v>60</v>
       </c>
       <c r="M20" s="13">
         <f>1000*I2*J20/(I20*L20)</f>
-        <v>4.39521800281294</v>
-      </c>
-    </row>
-    <row r="21" spans="2:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
+        <v>34.414556962025316</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B21" s="12">
         <v>90</v>
       </c>
@@ -1613,8 +1548,7 @@
       <c r="K21" s="10">
         <v>50</v>
       </c>
-      <c r="L21" s="3">
-        <f t="shared" si="1"/>
+      <c r="L21" s="10">
         <v>60</v>
       </c>
       <c r="M21" s="13">
@@ -1622,7 +1556,7 @@
         <v>3.9382482671707626</v>
       </c>
     </row>
-    <row r="22" spans="2:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B22" s="12">
         <v>95</v>
       </c>
@@ -1630,11 +1564,11 @@
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
       <c r="F22" s="7">
-        <f t="shared" ref="F22:H34" si="2">$B22-F$4*2</f>
+        <f t="shared" ref="F22:H34" si="1">$B22-F$4*2</f>
         <v>89</v>
       </c>
       <c r="G22" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>85</v>
       </c>
       <c r="H22" s="7"/>
@@ -1647,8 +1581,7 @@
       <c r="K22" s="10">
         <v>50</v>
       </c>
-      <c r="L22" s="3">
-        <f t="shared" si="1"/>
+      <c r="L22" s="10">
         <v>60</v>
       </c>
       <c r="M22" s="13">
@@ -1656,7 +1589,7 @@
         <v>3.3921302578018997</v>
       </c>
     </row>
-    <row r="23" spans="2:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B23" s="12">
         <v>100</v>
       </c>
@@ -1664,11 +1597,11 @@
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
       <c r="F23" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>94</v>
       </c>
       <c r="G23" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>90</v>
       </c>
       <c r="H23" s="7"/>
@@ -1681,8 +1614,7 @@
       <c r="K23" s="10">
         <v>50</v>
       </c>
-      <c r="L23" s="3">
-        <f t="shared" si="1"/>
+      <c r="L23" s="10">
         <v>60</v>
       </c>
       <c r="M23" s="13">
@@ -1690,7 +1622,7 @@
         <v>3.1102264244837023</v>
       </c>
     </row>
-    <row r="24" spans="2:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B24" s="12">
         <v>110</v>
       </c>
@@ -1698,11 +1630,11 @@
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
       <c r="F24" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>104</v>
       </c>
       <c r="G24" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="H24" s="7"/>
@@ -1715,8 +1647,7 @@
       <c r="K24" s="10">
         <v>50</v>
       </c>
-      <c r="L24" s="3">
-        <f t="shared" si="1"/>
+      <c r="L24" s="10">
         <v>60</v>
       </c>
       <c r="M24" s="13">
@@ -1724,7 +1655,7 @@
         <v>2.556237218813906</v>
       </c>
     </row>
-    <row r="25" spans="2:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B25" s="12">
         <v>120</v>
       </c>
@@ -1732,11 +1663,11 @@
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
       <c r="F25" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>114</v>
       </c>
       <c r="G25" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>110</v>
       </c>
       <c r="H25" s="7"/>
@@ -1749,8 +1680,7 @@
       <c r="K25" s="10">
         <v>50</v>
       </c>
-      <c r="L25" s="3">
-        <f t="shared" si="1"/>
+      <c r="L25" s="10">
         <v>60</v>
       </c>
       <c r="M25" s="13">
@@ -1758,7 +1688,7 @@
         <v>2.1378484693004958</v>
       </c>
     </row>
-    <row r="26" spans="2:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B26" s="12">
         <v>140</v>
       </c>
@@ -1766,11 +1696,11 @@
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
       <c r="F26" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>134</v>
       </c>
       <c r="G26" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>130</v>
       </c>
       <c r="H26" s="7"/>
@@ -1783,8 +1713,7 @@
       <c r="K26" s="10">
         <v>50</v>
       </c>
-      <c r="L26" s="3">
-        <f t="shared" si="1"/>
+      <c r="L26" s="10">
         <v>60</v>
       </c>
       <c r="M26" s="13">
@@ -1792,7 +1721,7 @@
         <v>1.5413070283600494</v>
       </c>
     </row>
-    <row r="27" spans="2:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B27" s="12">
         <v>160</v>
       </c>
@@ -1800,15 +1729,15 @@
       <c r="D27" s="7"/>
       <c r="E27" s="7"/>
       <c r="F27" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>154</v>
       </c>
       <c r="G27" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>150</v>
       </c>
       <c r="H27" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>144</v>
       </c>
       <c r="I27" s="7">
@@ -1820,8 +1749,7 @@
       <c r="K27" s="10">
         <v>50</v>
       </c>
-      <c r="L27" s="3">
-        <f t="shared" si="1"/>
+      <c r="L27" s="10">
         <v>60</v>
       </c>
       <c r="M27" s="13">
@@ -1829,7 +1757,7 @@
         <v>1.1950286806883366</v>
       </c>
     </row>
-    <row r="28" spans="2:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B28" s="12">
         <v>180</v>
       </c>
@@ -1837,15 +1765,15 @@
       <c r="D28" s="7"/>
       <c r="E28" s="7"/>
       <c r="F28" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>174</v>
       </c>
       <c r="G28" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>170</v>
       </c>
       <c r="H28" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>164</v>
       </c>
       <c r="I28" s="7">
@@ -1857,8 +1785,7 @@
       <c r="K28" s="10">
         <v>50</v>
       </c>
-      <c r="L28" s="3">
-        <f t="shared" si="1"/>
+      <c r="L28" s="10">
         <v>60</v>
       </c>
       <c r="M28" s="13">
@@ -1866,7 +1793,7 @@
         <v>0.93283582089552242</v>
       </c>
     </row>
-    <row r="29" spans="2:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B29" s="12">
         <v>200</v>
       </c>
@@ -1875,11 +1802,11 @@
       <c r="E29" s="7"/>
       <c r="F29" s="7"/>
       <c r="G29" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>190</v>
       </c>
       <c r="H29" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>184</v>
       </c>
       <c r="I29" s="7">
@@ -1891,8 +1818,7 @@
       <c r="K29" s="10">
         <v>50</v>
       </c>
-      <c r="L29" s="3">
-        <f t="shared" si="1"/>
+      <c r="L29" s="10">
         <v>60</v>
       </c>
       <c r="M29" s="13">
@@ -1900,7 +1826,7 @@
         <v>0.75165363800360796</v>
       </c>
     </row>
-    <row r="30" spans="2:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B30" s="12">
         <v>220</v>
       </c>
@@ -1909,11 +1835,11 @@
       <c r="E30" s="7"/>
       <c r="F30" s="7"/>
       <c r="G30" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>210</v>
       </c>
       <c r="H30" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>204</v>
       </c>
       <c r="I30" s="7">
@@ -1925,8 +1851,7 @@
       <c r="K30" s="10">
         <v>50</v>
       </c>
-      <c r="L30" s="3">
-        <f t="shared" si="1"/>
+      <c r="L30" s="10">
         <v>60</v>
       </c>
       <c r="M30" s="13">
@@ -1934,7 +1859,7 @@
         <v>0.62250996015936255</v>
       </c>
     </row>
-    <row r="31" spans="2:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B31" s="12">
         <v>240</v>
       </c>
@@ -1943,11 +1868,11 @@
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
       <c r="G31" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>230</v>
       </c>
       <c r="H31" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>224</v>
       </c>
       <c r="I31" s="7">
@@ -1959,8 +1884,7 @@
       <c r="K31" s="10">
         <v>50</v>
       </c>
-      <c r="L31" s="3">
-        <f t="shared" si="1"/>
+      <c r="L31" s="10">
         <v>60</v>
       </c>
       <c r="M31" s="13">
@@ -1968,7 +1892,7 @@
         <v>0.52521008403361347</v>
       </c>
     </row>
-    <row r="32" spans="2:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B32" s="12">
         <v>260</v>
       </c>
@@ -1977,11 +1901,11 @@
       <c r="E32" s="7"/>
       <c r="F32" s="7"/>
       <c r="G32" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>250</v>
       </c>
       <c r="H32" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>244</v>
       </c>
       <c r="I32" s="7">
@@ -1993,8 +1917,7 @@
       <c r="K32" s="10">
         <v>50</v>
       </c>
-      <c r="L32" s="3">
-        <f t="shared" si="1"/>
+      <c r="L32" s="10">
         <v>60</v>
       </c>
       <c r="M32" s="13">
@@ -2002,7 +1925,7 @@
         <v>0.44014084507042256</v>
       </c>
     </row>
-    <row r="33" spans="2:13" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B33" s="12">
         <v>300</v>
       </c>
@@ -2011,11 +1934,11 @@
       <c r="E33" s="7"/>
       <c r="F33" s="7"/>
       <c r="G33" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>290</v>
       </c>
       <c r="H33" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>284</v>
       </c>
       <c r="I33" s="7">
@@ -2024,11 +1947,10 @@
       <c r="J33" s="3">
         <v>1</v>
       </c>
-      <c r="K33" s="19">
-        <v>50</v>
-      </c>
-      <c r="L33" s="3">
-        <f t="shared" si="1"/>
+      <c r="K33" s="18">
+        <v>50</v>
+      </c>
+      <c r="L33" s="10">
         <v>60</v>
       </c>
       <c r="M33" s="13">
@@ -2036,7 +1958,7 @@
         <v>0.32748231595493843</v>
       </c>
     </row>
-    <row r="34" spans="2:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B34" s="14">
         <v>340</v>
       </c>
@@ -2046,7 +1968,7 @@
       <c r="F34" s="15"/>
       <c r="G34" s="15"/>
       <c r="H34" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>324</v>
       </c>
       <c r="I34" s="15">
@@ -2058,8 +1980,7 @@
       <c r="K34" s="4">
         <v>50</v>
       </c>
-      <c r="L34" s="17">
-        <f t="shared" si="1"/>
+      <c r="L34" s="10">
         <v>60</v>
       </c>
       <c r="M34" s="16">
